--- a/Docmentations/SIQs_Requirement.xlsx
+++ b/Docmentations/SIQs_Requirement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ITI\iti-Config-managment\Docmentations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B4BC161-91F4-454B-9804-6F7836F2BE5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{195C0243-DFDD-4194-8500-DA86D9F5B7BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B6544A6E-4D41-4CEF-9174-6A1D4B9FF080}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="147">
   <si>
     <t>ID</t>
   </si>
@@ -59,16 +59,25 @@
     <t>Req_SIQ_1</t>
   </si>
   <si>
+    <t>What happens after the successful registration?</t>
+  </si>
+  <si>
+    <t>A pop up message appear says "Account Created” and will be redirected to the home page</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Req_SIQ_2</t>
+  </si>
+  <si>
     <t>what are the nesseccary data for registeration?</t>
   </si>
   <si>
     <t>should have first name, last name, email and password</t>
   </si>
   <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Req_SIQ_2</t>
+    <t>Req_SIQ_3</t>
   </si>
   <si>
     <t>how to confirm that password is correct?</t>
@@ -77,7 +86,7 @@
     <t>should have at least one upper case letter, and must be at least 8 characters</t>
   </si>
   <si>
-    <t>Req_SIQ_3</t>
+    <t>Req_SIQ_4</t>
   </si>
   <si>
     <t>how to confirm that first name is correct?</t>
@@ -87,25 +96,25 @@
 must be not be blank</t>
   </si>
   <si>
-    <t>Req_SIQ_4</t>
+    <t>Req_SIQ_5</t>
   </si>
   <si>
     <t>how to confirm that last name is correct?</t>
   </si>
   <si>
-    <t>Req_SIQ_5</t>
+    <t>Req_SIQ_6</t>
   </si>
   <si>
     <t>What is the max lengh for the first and last name?</t>
   </si>
   <si>
-    <t>Req_SIQ_6</t>
+    <t>Req_SIQ_7</t>
   </si>
   <si>
     <t>What is the min lengh for the first and last name?</t>
   </si>
   <si>
-    <t>Req_SIQ_7</t>
+    <t>Req_SIQ_8</t>
   </si>
   <si>
     <t>how to confirm on registeration email?</t>
@@ -116,7 +125,7 @@
 doesn't contain space</t>
   </si>
   <si>
-    <t>Req_SIQ_8</t>
+    <t>Req_SIQ_9</t>
   </si>
   <si>
     <t>what happens when entering wrong data in registeration?</t>
@@ -128,7 +137,7 @@
     <t>LOGIN FEATURE FOR ALL TYPE OF USERS</t>
   </si>
   <si>
-    <t>Req_SIQ_9</t>
+    <t>Req_SIQ_10</t>
   </si>
   <si>
     <t>what does secure log in means?</t>
@@ -137,7 +146,7 @@
     <t>Login using email and password</t>
   </si>
   <si>
-    <t>Req_SIQ_10</t>
+    <t>Req_SIQ_11</t>
   </si>
   <si>
     <t xml:space="preserve">what happens when entering wrong mail or password in log in? </t>
@@ -149,7 +158,7 @@
     <t>CLIENT FEATURES</t>
   </si>
   <si>
-    <t>Req_SIQ_11</t>
+    <t>Req_SIQ_12</t>
   </si>
   <si>
     <t>the client can only buy or buy and sell?</t>
@@ -158,7 +167,7 @@
     <t>client account can only buy things</t>
   </si>
   <si>
-    <t>Req_SIQ_12</t>
+    <t>Req_SIQ_13</t>
   </si>
   <si>
     <t>Is the client account can act as a supplier or must have another account?</t>
@@ -167,25 +176,25 @@
     <t>must have another account</t>
   </si>
   <si>
-    <t>Req_SIQ_13</t>
+    <t>Req_SIQ_14</t>
   </si>
   <si>
     <t>what does product page contains?</t>
   </si>
   <si>
-    <t>each product should have a title, descripton,a picture, price and a purchasing button and add to cart</t>
-  </si>
-  <si>
-    <t>Req_SIQ_14</t>
+    <t>each product should have a title, descripton,a picture, price, add to cart button and an option to increase the quantity</t>
+  </si>
+  <si>
+    <t>Req_SIQ_15</t>
   </si>
   <si>
     <t>what does home page contain?</t>
   </si>
   <si>
-    <t>products and their title,price and image, view cart</t>
-  </si>
-  <si>
-    <t>Req_SIQ_15</t>
+    <t>products and their title,price and image, view cart and view history</t>
+  </si>
+  <si>
+    <t>Req_SIQ_16</t>
   </si>
   <si>
     <t>What happens when the client try to add out of stock product?</t>
@@ -194,7 +203,7 @@
     <t>A pop up message appears says: "Out of stock"</t>
   </si>
   <si>
-    <t>Req_SIQ_16</t>
+    <t>Req_SIQ_17</t>
   </si>
   <si>
     <t>What happens if the client try to access the history page when he has no purchases?</t>
@@ -203,7 +212,7 @@
     <t>He will redirected to the history page with a message in it says: "No purchases yet"</t>
   </si>
   <si>
-    <t>Req_SIQ_17</t>
+    <t>Req_SIQ_18</t>
   </si>
   <si>
     <t>Will be there a confirmation message when the client add a product to cart?</t>
@@ -212,16 +221,16 @@
     <t>No the product will be added to the cart without confirmation message but the number next to cart icon will increase</t>
   </si>
   <si>
-    <t>Req_SIQ_18</t>
+    <t>Req_SIQ_19</t>
   </si>
   <si>
     <t>Will be there a confirmation message when the client delete a product from the cart?</t>
   </si>
   <si>
-    <t>No the product will be removed from the cart without confirmation message</t>
-  </si>
-  <si>
-    <t>Req_SIQ_19</t>
+    <t>No the product will be removed from the cart without confirmation message but the number next to cart icon will decrease</t>
+  </si>
+  <si>
+    <t>Req_SIQ_20</t>
   </si>
   <si>
     <t>What happens when pressing on the checkout button in the cart page?</t>
@@ -230,25 +239,25 @@
     <t>Will be redirected to the payment page</t>
   </si>
   <si>
-    <t>Req_SIQ_20</t>
-  </si>
-  <si>
-    <t>What happens when the client press on the checkout button when the cart has no products on it?</t>
-  </si>
-  <si>
-    <t>A pop up message appears says: "Please add a product to the cart first"</t>
-  </si>
-  <si>
     <t>Req_SIQ_21</t>
   </si>
   <si>
+    <t>What will exist when the client goes to the cart page when the cart has no products on it?</t>
+  </si>
+  <si>
+    <t>There wiil be a message in the page says: "Your cart is empty. Continue shopping ". Continue shopping will be a link that redirect to the home page</t>
+  </si>
+  <si>
+    <t>Req_SIQ_22</t>
+  </si>
+  <si>
     <t>Will the payment method be cash only?</t>
   </si>
   <si>
     <t>Yes, the system supports cash-only payments. No online or card payment options are available</t>
   </si>
   <si>
-    <t>Req_SIQ_22</t>
+    <t>Req_SIQ_23</t>
   </si>
   <si>
     <t>What will be in the Payment Page?</t>
@@ -257,7 +266,7 @@
     <t>There will be phone number,city and full address</t>
   </si>
   <si>
-    <t>Req_SIQ_23</t>
+    <t>Req_SIQ_24</t>
   </si>
   <si>
     <t>What are the validations for the client’s phone number?</t>
@@ -266,46 +275,55 @@
     <t>Not blank and has exact 11 numbers</t>
   </si>
   <si>
-    <t>Req_SIQ_24</t>
+    <t>Req_SIQ_25</t>
   </si>
   <si>
     <t>What are the validations for the city?</t>
   </si>
   <si>
-    <t>Not blank and accepts only the predefined values</t>
-  </si>
-  <si>
-    <t>Req_SIQ_25</t>
+    <t>Has a default value (Select a city) but accepts only the predefined values (Cairo, Alexandria, Giza)</t>
+  </si>
+  <si>
+    <t>Req_SIQ_26</t>
   </si>
   <si>
     <t>What are the validations for the client’s address?</t>
   </si>
   <si>
-    <t>Not blank and has minimum length of 10 characters</t>
-  </si>
-  <si>
-    <t>Req_SIQ_26</t>
+    <t>Not blank, has minimum length of 10 characters and maximum length of 200 characters</t>
+  </si>
+  <si>
+    <t>Req_SIQ_27</t>
+  </si>
+  <si>
+    <t>What happens when the data in the payment page is invalid or missing?</t>
+  </si>
+  <si>
+    <t>A pop up message appear says "Invalid data”</t>
+  </si>
+  <si>
+    <t>Req_SIQ_28</t>
   </si>
   <si>
     <t>What happens when the client press on the place order button which appears in the payment page?</t>
   </si>
   <si>
-    <t>A pop up message appears says: "You have completed your purchase successfully" and the product appears in the history page and is removed from the cart</t>
+    <t>A pop up message appears says: "Order Placed" and the product appears in the history page and is removed from the cart</t>
   </si>
   <si>
     <t>SUPPLIER FEATURES</t>
   </si>
   <si>
+    <t>Req_SIQ_29</t>
+  </si>
+  <si>
     <t>do suppliers appear in the purchasing process or just to the admin?</t>
   </si>
   <si>
     <t>the supplier name wouldn't appear on the product page</t>
   </si>
   <si>
-    <t>no client must know the supplier</t>
-  </si>
-  <si>
-    <t>Req_SIQ_27</t>
+    <t>Req_SIQ_30</t>
   </si>
   <si>
     <t>what are the supplier's features?</t>
@@ -315,7 +333,7 @@
 and can delete his products, view his product</t>
   </si>
   <si>
-    <t>Req_SIQ_28</t>
+    <t>Req_SIQ_31</t>
   </si>
   <si>
     <t>What are the product title validations?</t>
@@ -324,25 +342,25 @@
     <t>Not blank, has a max of 100 character, has a minimum of 10 and doesn't contain special characters</t>
   </si>
   <si>
-    <t>Req_SIQ_29</t>
+    <t>Req_SIQ_32</t>
   </si>
   <si>
     <t>What are the product description validations?</t>
   </si>
   <si>
-    <t>Not blank, has a max of 2000 character, has a minimum of 10 and doesn't contain special characters</t>
-  </si>
-  <si>
-    <t>Req_SIQ_30</t>
-  </si>
-  <si>
-    <t>What are the product price validations?</t>
-  </si>
-  <si>
-    <t>Not blank and has only positive numbers</t>
-  </si>
-  <si>
-    <t>Req_SIQ_31</t>
+    <t>Not blank, has a max of 800 character, has a minimum of 10 and doesn't contain special characters</t>
+  </si>
+  <si>
+    <t>Req_SIQ_33</t>
+  </si>
+  <si>
+    <t>What are the product price and quantity validations?</t>
+  </si>
+  <si>
+    <t>Not blank, not zero and has only positive numbers but the difference is that quantity is an integer</t>
+  </si>
+  <si>
+    <t>Req_SIQ_34</t>
   </si>
   <si>
     <t>What are the product image validations?</t>
@@ -351,16 +369,16 @@
     <t>Not blank, of type: (jpg, jpeg or png) and has a maximum size of 10 MB</t>
   </si>
   <si>
-    <t>Req_SIQ_32</t>
+    <t>Req_SIQ_35</t>
   </si>
   <si>
     <t>What happens when the product data is invalid or missing?</t>
   </si>
   <si>
-    <t>A pop up message appear says "Invalid data”</t>
-  </si>
-  <si>
-    <t>Req_SIQ_33</t>
+    <t>A pop up message appear says "Invalid data” and for the image you won't be able to choose anything other than jpg/jpeg/png.</t>
+  </si>
+  <si>
+    <t>Req_SIQ_36</t>
   </si>
   <si>
     <t>What happens after the supplier add a product?</t>
@@ -369,7 +387,7 @@
     <t>A pop up message appear says "Product has been added successfully” and the product will be added to list of products in the supplier dashboard</t>
   </si>
   <si>
-    <t>Req_SIQ_34</t>
+    <t>Req_SIQ_37</t>
   </si>
   <si>
     <t>What happens after the supplier delete a product?</t>
@@ -378,34 +396,22 @@
     <t>A pop up message appear says "Product has been deleted successfully”</t>
   </si>
   <si>
-    <t>Req_SIQ_35</t>
-  </si>
-  <si>
-    <t>What happens if the supplier tried to add a product with the same data as a previous product?</t>
-  </si>
-  <si>
-    <t>A pop up message appear says "Product with these data already exists”</t>
-  </si>
-  <si>
     <t>ADMIN FEATURES</t>
   </si>
   <si>
-    <t>Req_SIQ_36</t>
+    <t>Req_SIQ_38</t>
   </si>
   <si>
     <t>can admin add or delete and supplier accounts?</t>
   </si>
   <si>
-    <t>Req_SIQ_37</t>
+    <t>Req_SIQ_39</t>
   </si>
   <si>
     <t>is there only one admin to the website?</t>
   </si>
   <si>
-    <t>no 2</t>
-  </si>
-  <si>
-    <t>Req_SIQ_38</t>
+    <t>Req_SIQ_40</t>
   </si>
   <si>
     <t xml:space="preserve">what should be in the dashboard of the admin?
@@ -415,13 +421,13 @@
     <t>a list of the existing clients and suppliers</t>
   </si>
   <si>
-    <t>Req_SIQ_39</t>
+    <t>Req_SIQ_41</t>
   </si>
   <si>
     <t>can admin delete an existing client account?</t>
   </si>
   <si>
-    <t>Req_SIQ_40</t>
+    <t>Req_SIQ_42</t>
   </si>
   <si>
     <t>What happens after the admin add a supplier?</t>
@@ -430,7 +436,7 @@
     <t>A pop up message appear says "Supplier added successfully” and the supplier account will appear at the list of accounts in the admin dashboard</t>
   </si>
   <si>
-    <t>Req_SIQ_41</t>
+    <t>Req_SIQ_43</t>
   </si>
   <si>
     <t>What happens after the admin delete a supplier or client account?</t>
@@ -439,16 +445,16 @@
     <t>A pop up message appear says "Account deleted successfully”</t>
   </si>
   <si>
-    <t>Req_SIQ_42</t>
-  </si>
-  <si>
-    <t>What happens if the admin tried to add a supplier with the same data as a previous supplier?</t>
-  </si>
-  <si>
-    <t>A pop up message appear says "Supplier with these data already exists”</t>
-  </si>
-  <si>
-    <t>Req_SIQ_43</t>
+    <t>Req_SIQ_44</t>
+  </si>
+  <si>
+    <t>What happens if the admin tried to add a supplier with the same email as a previous supplier?</t>
+  </si>
+  <si>
+    <t>A pop up message appear says "Supplier with these data already exists.”</t>
+  </si>
+  <si>
+    <t>Req_SIQ_45</t>
   </si>
   <si>
     <t>What should appear at the supplier or admin dashboard if it is empty?</t>
@@ -460,16 +466,16 @@
     <t>WEB PAGE FEATURES</t>
   </si>
   <si>
-    <t>Req_SIQ_44</t>
+    <t>Req_SIQ_46</t>
   </si>
   <si>
     <t>what should be the first page to appear upon accessing the website?</t>
   </si>
   <si>
-    <t>open on the log in and sign up page and back to the login page then navigate to the home page</t>
-  </si>
-  <si>
-    <t>Req_SIQ_45</t>
+    <t>log in page will appear first and from the login page, the client can go to the sign up page or if he logged in successfuly, will be redirected to the home page</t>
+  </si>
+  <si>
+    <t>Req_SIQ_47</t>
   </si>
   <si>
     <t>what language to be displayed with?</t>
@@ -482,7 +488,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -530,8 +536,19 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -568,6 +585,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -596,7 +619,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -635,6 +658,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -977,18 +1018,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2F2C9DE-B329-40FD-AE6F-FBEC99EE2B97}">
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.85546875" style="4" customWidth="1"/>
     <col min="2" max="2" width="44.42578125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="53.85546875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="56.5703125" style="4" customWidth="1"/>
     <col min="4" max="4" width="26.85546875" style="4" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" style="4" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" ht="52.5" customHeight="1">
+    <row r="1" spans="1:13" s="3" customFormat="1" ht="52.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1005,655 +1046,708 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="49.5" customHeight="1">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:13" ht="49.5" customHeight="1">
+      <c r="A2" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-    </row>
-    <row r="3" spans="1:12" ht="65.25" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+    </row>
+    <row r="3" spans="1:13" s="9" customFormat="1" ht="60.75" customHeight="1">
+      <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-    </row>
-    <row r="4" spans="1:12" ht="65.25" customHeight="1">
-      <c r="A4" s="6" t="s">
+      <c r="D3" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="17"/>
+    </row>
+    <row r="4" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-    </row>
-    <row r="5" spans="1:12" ht="65.25" customHeight="1">
-      <c r="A5" s="5" t="s">
+      <c r="D4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="16"/>
+    </row>
+    <row r="5" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-    </row>
-    <row r="6" spans="1:12" ht="65.25" customHeight="1">
-      <c r="A6" s="6" t="s">
+      <c r="D5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+    </row>
+    <row r="6" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-    </row>
-    <row r="7" spans="1:12" ht="65.25" customHeight="1">
-      <c r="A7" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="D6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+    </row>
+    <row r="7" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="7">
+      <c r="B7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-    </row>
-    <row r="8" spans="1:12" ht="65.25" customHeight="1">
-      <c r="A8" s="6" t="s">
+      <c r="C7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+    </row>
+    <row r="8" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="7">
         <v>20</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="6">
+      <c r="D8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="7"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="6">
         <v>2</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-    </row>
-    <row r="9" spans="1:12" ht="65.25" customHeight="1">
-      <c r="A9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-    </row>
-    <row r="10" spans="1:12" ht="65.25" customHeight="1">
-      <c r="A10" s="6" t="s">
+      <c r="D9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+    </row>
+    <row r="10" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-    </row>
-    <row r="11" spans="1:12" ht="51" customHeight="1">
-      <c r="A11" s="14" t="s">
+      <c r="D10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+    </row>
+    <row r="11" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-    </row>
-    <row r="12" spans="1:12" ht="65.25" customHeight="1">
-      <c r="A12" s="6" t="s">
+      <c r="B11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="C11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="D11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+    </row>
+    <row r="12" spans="1:13" ht="51" customHeight="1">
+      <c r="A12" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-    </row>
-    <row r="13" spans="1:12" ht="65.25" customHeight="1">
-      <c r="A13" s="5" t="s">
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+    </row>
+    <row r="13" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A13" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-    </row>
-    <row r="14" spans="1:12" ht="48.75" customHeight="1">
-      <c r="A14" s="14" t="s">
+      <c r="D13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+    </row>
+    <row r="14" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A14" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-    </row>
-    <row r="15" spans="1:12" ht="65.25" customHeight="1">
-      <c r="A15" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+    </row>
+    <row r="15" spans="1:13" ht="48.75" customHeight="1">
+      <c r="A15" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-    </row>
-    <row r="16" spans="1:12" ht="65.25" customHeight="1">
-      <c r="A16" s="8" t="s">
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+    </row>
+    <row r="16" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
+      <c r="D16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
     </row>
     <row r="17" spans="1:13" ht="65.25" customHeight="1">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
+      <c r="D17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
     </row>
     <row r="18" spans="1:13" ht="65.25" customHeight="1">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-    </row>
-    <row r="19" spans="1:13" s="9" customFormat="1" ht="65.25" customHeight="1">
-      <c r="A19" s="7" t="s">
+      <c r="D18" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+    </row>
+    <row r="19" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A19" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-    </row>
-    <row r="20" spans="1:13" ht="65.25" customHeight="1">
-      <c r="A20" s="8" t="s">
+      <c r="D19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+    </row>
+    <row r="20" spans="1:13" s="9" customFormat="1" ht="65.25" customHeight="1">
+      <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-    </row>
-    <row r="21" spans="1:13" s="9" customFormat="1" ht="65.25" customHeight="1">
-      <c r="A21" s="7" t="s">
+      <c r="D20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A21" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:13" ht="65.25" customHeight="1">
-      <c r="A22" s="8" t="s">
+      <c r="D21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+    </row>
+    <row r="22" spans="1:13" s="9" customFormat="1" ht="65.25" customHeight="1">
+      <c r="A22" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
-    </row>
-    <row r="23" spans="1:13" s="13" customFormat="1" ht="65.25" customHeight="1">
-      <c r="A23" s="7" t="s">
+      <c r="D22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="7"/>
+    </row>
+    <row r="23" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A23" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-    </row>
-    <row r="24" spans="1:13" ht="65.25" customHeight="1">
-      <c r="A24" s="8" t="s">
+      <c r="D23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="6"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="16"/>
+    </row>
+    <row r="24" spans="1:13" s="13" customFormat="1" ht="65.25" customHeight="1">
+      <c r="A24" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="13"/>
-    </row>
-    <row r="25" spans="1:13" s="12" customFormat="1" ht="65.25" customHeight="1">
-      <c r="A25" s="7" t="s">
+      <c r="D24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="7"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
+    </row>
+    <row r="25" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A25" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="13"/>
-      <c r="M25" s="13"/>
+      <c r="D25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="16"/>
     </row>
     <row r="26" spans="1:13" s="12" customFormat="1" ht="65.25" customHeight="1">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="13"/>
+      <c r="D26" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="7"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
     </row>
     <row r="27" spans="1:13" s="12" customFormat="1" ht="65.25" customHeight="1">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
-      <c r="M27" s="13"/>
-    </row>
-    <row r="28" spans="1:13" s="13" customFormat="1" ht="65.25" customHeight="1">
-      <c r="A28" s="8" t="s">
+      <c r="D27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+    </row>
+    <row r="28" spans="1:13" s="12" customFormat="1" ht="65.25" customHeight="1">
+      <c r="A28" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-    </row>
-    <row r="29" spans="1:13" s="12" customFormat="1" ht="65.25" customHeight="1">
-      <c r="A29" s="7" t="s">
+      <c r="D28" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="7"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+    </row>
+    <row r="29" spans="1:13" s="13" customFormat="1" ht="65.25" customHeight="1">
+      <c r="A29" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
-    </row>
-    <row r="30" spans="1:13" s="9" customFormat="1" ht="65.25" customHeight="1">
-      <c r="A30" s="8" t="s">
+      <c r="D29" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="8"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
+      <c r="M29" s="16"/>
+    </row>
+    <row r="30" spans="1:13" s="12" customFormat="1" ht="65.25" customHeight="1">
+      <c r="A30" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-    </row>
-    <row r="31" spans="1:13" ht="48" customHeight="1">
-      <c r="A31" s="14" t="s">
+      <c r="D30" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="7"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="16"/>
+    </row>
+    <row r="31" spans="1:13" s="14" customFormat="1" ht="65.25" customHeight="1">
+      <c r="A31" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="13"/>
-      <c r="M31" s="13"/>
-    </row>
-    <row r="32" spans="1:13" ht="65.25" customHeight="1">
-      <c r="A32" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B32" s="6" t="s">
+      <c r="B31" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C31" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D31" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="15"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16"/>
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+      <c r="M31" s="16"/>
+    </row>
+    <row r="32" spans="1:13" s="9" customFormat="1" ht="65.25" customHeight="1">
+      <c r="A32" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E32" s="6"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
-      <c r="M32" s="13"/>
-    </row>
-    <row r="33" spans="1:13" ht="65.25" customHeight="1">
-      <c r="A33" s="7" t="s">
+      <c r="B32" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C32" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="D32" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" spans="1:13" ht="48" customHeight="1">
+      <c r="A33" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="13"/>
-      <c r="M33" s="13"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+      <c r="M33" s="16"/>
     </row>
     <row r="34" spans="1:13" ht="65.25" customHeight="1">
       <c r="A34" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="13"/>
-      <c r="M34" s="13"/>
+      <c r="D34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="6"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="16"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+      <c r="M34" s="16"/>
     </row>
     <row r="35" spans="1:13" ht="65.25" customHeight="1">
       <c r="A35" s="7" t="s">
@@ -1665,16 +1759,18 @@
       <c r="C35" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="D35" s="5"/>
+      <c r="D35" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="E35" s="5"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="13"/>
-      <c r="M35" s="13"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+      <c r="M35" s="16"/>
     </row>
     <row r="36" spans="1:13" ht="65.25" customHeight="1">
       <c r="A36" s="6" t="s">
@@ -1686,16 +1782,18 @@
       <c r="C36" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D36" s="8"/>
+      <c r="D36" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="E36" s="8"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
-      <c r="M36" s="13"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="16"/>
     </row>
     <row r="37" spans="1:13" ht="65.25" customHeight="1">
       <c r="A37" s="7" t="s">
@@ -1707,16 +1805,18 @@
       <c r="C37" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D37" s="5"/>
+      <c r="D37" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="E37" s="5"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="13"/>
-      <c r="M37" s="13"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="16"/>
     </row>
     <row r="38" spans="1:13" ht="65.25" customHeight="1">
       <c r="A38" s="6" t="s">
@@ -1728,16 +1828,18 @@
       <c r="C38" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="D38" s="8"/>
+      <c r="D38" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="E38" s="8"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="13"/>
-      <c r="M38" s="13"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="16"/>
     </row>
     <row r="39" spans="1:13" ht="65.25" customHeight="1">
       <c r="A39" s="7" t="s">
@@ -1749,16 +1851,18 @@
       <c r="C39" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D39" s="5"/>
+      <c r="D39" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="E39" s="5"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
-      <c r="L39" s="13"/>
-      <c r="M39" s="13"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+      <c r="J39" s="16"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="16"/>
     </row>
     <row r="40" spans="1:13" ht="65.25" customHeight="1">
       <c r="A40" s="6" t="s">
@@ -1770,16 +1874,18 @@
       <c r="C40" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="D40" s="8"/>
+      <c r="D40" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="E40" s="8"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="13"/>
-      <c r="K40" s="13"/>
-      <c r="L40" s="13"/>
-      <c r="M40" s="13"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="16"/>
     </row>
     <row r="41" spans="1:13" ht="65.25" customHeight="1">
       <c r="A41" s="7" t="s">
@@ -1791,271 +1897,289 @@
       <c r="C41" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D41" s="5"/>
+      <c r="D41" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="E41" s="5"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="13"/>
-      <c r="K41" s="13"/>
-      <c r="L41" s="13"/>
-      <c r="M41" s="13"/>
-    </row>
-    <row r="42" spans="1:13" ht="48" customHeight="1">
-      <c r="A42" s="14" t="s">
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="16"/>
+      <c r="J41" s="16"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+      <c r="M41" s="16"/>
+    </row>
+    <row r="42" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A42" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="13"/>
-      <c r="J42" s="13"/>
-      <c r="K42" s="13"/>
-      <c r="L42" s="13"/>
-      <c r="M42" s="13"/>
-    </row>
-    <row r="43" spans="1:13" ht="65.25" customHeight="1">
-      <c r="A43" s="5" t="s">
+      <c r="B42" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="C42" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E43" s="5"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="13"/>
-      <c r="K43" s="13"/>
-      <c r="L43" s="13"/>
-      <c r="M43" s="13"/>
+      <c r="D42" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="8"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="16"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+      <c r="M42" s="16"/>
+    </row>
+    <row r="43" spans="1:13" ht="48" customHeight="1">
+      <c r="A43" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="16"/>
+      <c r="H43" s="16"/>
+      <c r="I43" s="16"/>
+      <c r="J43" s="16"/>
+      <c r="K43" s="16"/>
+      <c r="L43" s="16"/>
+      <c r="M43" s="16"/>
     </row>
     <row r="44" spans="1:13" ht="65.25" customHeight="1">
-      <c r="A44" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B44" s="6" t="s">
+      <c r="A44" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="6" t="s">
+      <c r="B44" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E44" s="6"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="13"/>
-      <c r="K44" s="13"/>
-      <c r="L44" s="13"/>
-      <c r="M44" s="13"/>
+      <c r="C44" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="5"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="16"/>
+      <c r="J44" s="16"/>
+      <c r="K44" s="16"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="16"/>
     </row>
     <row r="45" spans="1:13" ht="65.25" customHeight="1">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="6"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+    </row>
+    <row r="46" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A46" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D45" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="13"/>
-      <c r="K45" s="13"/>
-      <c r="L45" s="13"/>
-      <c r="M45" s="13"/>
-    </row>
-    <row r="46" spans="1:13" ht="65.25" customHeight="1">
-      <c r="A46" s="8" t="s">
+      <c r="B46" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="C46" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" s="6"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
-      <c r="J46" s="13"/>
-      <c r="K46" s="13"/>
-      <c r="L46" s="13"/>
-      <c r="M46" s="13"/>
+      <c r="D46" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="5"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="16"/>
+      <c r="H46" s="16"/>
+      <c r="I46" s="16"/>
+      <c r="J46" s="16"/>
+      <c r="K46" s="16"/>
+      <c r="L46" s="16"/>
+      <c r="M46" s="16"/>
     </row>
     <row r="47" spans="1:13" ht="65.25" customHeight="1">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="6"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="16"/>
+      <c r="H47" s="16"/>
+      <c r="I47" s="16"/>
+      <c r="J47" s="16"/>
+      <c r="K47" s="16"/>
+      <c r="L47" s="16"/>
+      <c r="M47" s="16"/>
+    </row>
+    <row r="48" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A48" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="13"/>
-      <c r="J47" s="13"/>
-      <c r="K47" s="13"/>
-      <c r="L47" s="13"/>
-      <c r="M47" s="13"/>
-    </row>
-    <row r="48" spans="1:13" ht="65.25" customHeight="1">
-      <c r="A48" s="8" t="s">
+      <c r="B48" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="C48" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="D48" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" s="7"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="16"/>
+      <c r="I48" s="16"/>
+      <c r="J48" s="16"/>
+      <c r="K48" s="16"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
+    </row>
+    <row r="49" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A49" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="13"/>
-      <c r="K48" s="13"/>
-      <c r="L48" s="13"/>
-      <c r="M48" s="13"/>
-    </row>
-    <row r="49" spans="1:13" s="9" customFormat="1" ht="65.25" customHeight="1">
-      <c r="A49" s="5" t="s">
+      <c r="B49" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="C49" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="D49" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="6"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="16"/>
+      <c r="J49" s="16"/>
+      <c r="K49" s="16"/>
+      <c r="L49" s="16"/>
+      <c r="M49" s="16"/>
+    </row>
+    <row r="50" spans="1:13" s="9" customFormat="1" ht="65.25" customHeight="1">
+      <c r="A50" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-    </row>
-    <row r="50" spans="1:13" ht="65.25" customHeight="1">
-      <c r="A50" s="8" t="s">
+      <c r="B50" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="C50" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="D50" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="7"/>
+    </row>
+    <row r="51" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A51" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="13"/>
-      <c r="K50" s="13"/>
-      <c r="L50" s="13"/>
-      <c r="M50" s="13"/>
-    </row>
-    <row r="51" spans="1:13" ht="48" customHeight="1">
-      <c r="A51" s="14" t="s">
+      <c r="B51" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="13"/>
-      <c r="K51" s="13"/>
-      <c r="L51" s="13"/>
-      <c r="M51" s="13"/>
-    </row>
-    <row r="52" spans="1:13" ht="65.25" customHeight="1">
-      <c r="A52" s="6" t="s">
+      <c r="C51" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="D51" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="6"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
+      <c r="H51" s="16"/>
+      <c r="I51" s="16"/>
+      <c r="J51" s="16"/>
+      <c r="K51" s="16"/>
+      <c r="L51" s="16"/>
+      <c r="M51" s="16"/>
+    </row>
+    <row r="52" spans="1:13" ht="48" customHeight="1">
+      <c r="A52" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="B52" s="20"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="16"/>
+      <c r="I52" s="16"/>
+      <c r="J52" s="16"/>
+      <c r="K52" s="16"/>
+      <c r="L52" s="16"/>
+      <c r="M52" s="16"/>
+    </row>
+    <row r="53" spans="1:13" ht="65.25" customHeight="1">
+      <c r="A53" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E52" s="6"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="13"/>
-      <c r="K52" s="13"/>
-      <c r="L52" s="13"/>
-      <c r="M52" s="13"/>
-    </row>
-    <row r="53" spans="1:13" ht="65.25" customHeight="1">
-      <c r="A53" s="7" t="s">
+      <c r="B53" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="C53" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="D53" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="6"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="16"/>
+      <c r="H53" s="16"/>
+      <c r="I53" s="16"/>
+      <c r="J53" s="16"/>
+      <c r="K53" s="16"/>
+      <c r="L53" s="16"/>
+      <c r="M53" s="16"/>
+    </row>
+    <row r="54" spans="1:13" s="9" customFormat="1" ht="65.25" customHeight="1">
+      <c r="A54" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D53" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" s="5"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="13"/>
-      <c r="J53" s="13"/>
-      <c r="K53" s="13"/>
-      <c r="L53" s="13"/>
-      <c r="M53" s="13"/>
-    </row>
-    <row r="54" spans="1:13" s="9" customFormat="1">
-      <c r="A54" s="11"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
+      <c r="B54" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" s="7"/>
     </row>
     <row r="55" spans="1:13" s="9" customFormat="1">
       <c r="A55" s="11"/>
@@ -2065,18 +2189,18 @@
       <c r="E55" s="11"/>
     </row>
     <row r="56" spans="1:13" s="9" customFormat="1">
-      <c r="A56" s="7"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
+      <c r="A56" s="11"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
     </row>
     <row r="57" spans="1:13" s="9" customFormat="1">
-      <c r="A57" s="11"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
+      <c r="A57" s="7"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
     </row>
     <row r="58" spans="1:13" s="9" customFormat="1">
       <c r="A58" s="11"/>
@@ -2086,11 +2210,11 @@
       <c r="E58" s="11"/>
     </row>
     <row r="59" spans="1:13" s="9" customFormat="1">
-      <c r="A59" s="7"/>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
+      <c r="A59" s="11"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="11"/>
     </row>
     <row r="60" spans="1:13" s="9" customFormat="1">
       <c r="A60" s="7"/>
@@ -2169,30 +2293,97 @@
       <c r="D70" s="7"/>
       <c r="E70" s="7"/>
     </row>
-    <row r="71" spans="1:13">
-      <c r="A71" s="13"/>
-      <c r="B71" s="13"/>
-      <c r="C71" s="13"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="13"/>
-      <c r="J71" s="13"/>
-      <c r="K71" s="13"/>
-      <c r="L71" s="13"/>
-      <c r="M71" s="13"/>
+    <row r="71" spans="1:13" s="9" customFormat="1">
+      <c r="A71" s="7"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
+    </row>
+    <row r="72" spans="1:13">
+      <c r="A72" s="16"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="16"/>
+      <c r="D72" s="16"/>
+      <c r="E72" s="16"/>
+      <c r="F72" s="16"/>
+      <c r="G72" s="16"/>
+      <c r="H72" s="16"/>
+      <c r="I72" s="16"/>
+      <c r="J72" s="16"/>
+      <c r="K72" s="16"/>
+      <c r="L72" s="16"/>
+      <c r="M72" s="16"/>
+    </row>
+    <row r="73" spans="1:13">
+      <c r="A73" s="16"/>
+      <c r="B73" s="16"/>
+      <c r="C73" s="16"/>
+      <c r="D73" s="16"/>
+      <c r="E73" s="16"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="16"/>
+      <c r="H73" s="16"/>
+      <c r="I73" s="16"/>
+      <c r="J73" s="16"/>
+      <c r="K73" s="16"/>
+      <c r="L73" s="16"/>
+      <c r="M73" s="16"/>
+    </row>
+    <row r="74" spans="1:13">
+      <c r="A74" s="16"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16"/>
+      <c r="H74" s="16"/>
+      <c r="I74" s="16"/>
+      <c r="J74" s="16"/>
+      <c r="K74" s="16"/>
+      <c r="L74" s="16"/>
+      <c r="M74" s="16"/>
+    </row>
+    <row r="75" spans="1:13">
+      <c r="A75" s="16"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="16"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="16"/>
+      <c r="H75" s="16"/>
+      <c r="I75" s="16"/>
+      <c r="J75" s="16"/>
+      <c r="K75" s="16"/>
+      <c r="L75" s="16"/>
+      <c r="M75" s="16"/>
+    </row>
+    <row r="76" spans="1:13">
+      <c r="A76" s="16"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="16"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="16"/>
+      <c r="H76" s="16"/>
+      <c r="I76" s="16"/>
+      <c r="J76" s="16"/>
+      <c r="K76" s="16"/>
+      <c r="L76" s="16"/>
+      <c r="M76" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="J4:L4"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A33:E33"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
